--- a/cluster.xlsx
+++ b/cluster.xlsx
@@ -429,7 +429,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H507"/>
+  <dimension ref="A1:H538"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -13528,25 +13528,25 @@
     </row>
     <row r="504">
       <c r="A504" s="2" t="n">
-        <v>46076</v>
+        <v>46075</v>
       </c>
       <c r="B504" t="n">
-        <v>64656.02</v>
+        <v>67643.39999999999</v>
       </c>
       <c r="C504" t="n">
-        <v>9</v>
+        <v>2</v>
       </c>
       <c r="D504" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="E504" t="n">
-        <v>7</v>
+        <v>10</v>
       </c>
       <c r="F504" t="n">
-        <v>5</v>
+        <v>12</v>
       </c>
       <c r="G504" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="H504" t="n">
         <v>10</v>
@@ -13554,10 +13554,10 @@
     </row>
     <row r="505">
       <c r="A505" s="2" t="n">
-        <v>46078</v>
+        <v>46076</v>
       </c>
       <c r="B505" t="n">
-        <v>67988.03999999999</v>
+        <v>64656.02</v>
       </c>
       <c r="C505" t="n">
         <v>9</v>
@@ -13580,16 +13580,16 @@
     </row>
     <row r="506">
       <c r="A506" s="2" t="n">
-        <v>46080</v>
+        <v>46077</v>
       </c>
       <c r="B506" t="n">
-        <v>65872.10000000001</v>
+        <v>64058.15</v>
       </c>
       <c r="C506" t="n">
         <v>9</v>
       </c>
       <c r="D506" t="n">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="E506" t="n">
         <v>7</v>
@@ -13606,28 +13606,834 @@
     </row>
     <row r="507">
       <c r="A507" s="2" t="n">
+        <v>46078</v>
+      </c>
+      <c r="B507" t="n">
+        <v>67988.03999999999</v>
+      </c>
+      <c r="C507" t="n">
+        <v>9</v>
+      </c>
+      <c r="D507" t="n">
+        <v>3</v>
+      </c>
+      <c r="E507" t="n">
+        <v>7</v>
+      </c>
+      <c r="F507" t="n">
+        <v>0</v>
+      </c>
+      <c r="G507" t="n">
+        <v>1</v>
+      </c>
+      <c r="H507" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="508">
+      <c r="A508" s="2" t="n">
+        <v>46079</v>
+      </c>
+      <c r="B508" t="n">
+        <v>67485.17999999999</v>
+      </c>
+      <c r="C508" t="n">
+        <v>1</v>
+      </c>
+      <c r="D508" t="n">
+        <v>3</v>
+      </c>
+      <c r="E508" t="n">
+        <v>7</v>
+      </c>
+      <c r="F508" t="n">
+        <v>0</v>
+      </c>
+      <c r="G508" t="n">
+        <v>1</v>
+      </c>
+      <c r="H508" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="509">
+      <c r="A509" s="2" t="n">
+        <v>46080</v>
+      </c>
+      <c r="B509" t="n">
+        <v>65872.10000000001</v>
+      </c>
+      <c r="C509" t="n">
+        <v>1</v>
+      </c>
+      <c r="D509" t="n">
+        <v>3</v>
+      </c>
+      <c r="E509" t="n">
+        <v>7</v>
+      </c>
+      <c r="F509" t="n">
+        <v>12</v>
+      </c>
+      <c r="G509" t="n">
+        <v>1</v>
+      </c>
+      <c r="H509" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="510">
+      <c r="A510" s="2" t="n">
+        <v>46081</v>
+      </c>
+      <c r="B510" t="n">
+        <v>66973.25999999999</v>
+      </c>
+      <c r="C510" t="n">
+        <v>1</v>
+      </c>
+      <c r="D510" t="n">
+        <v>3</v>
+      </c>
+      <c r="E510" t="n">
+        <v>6</v>
+      </c>
+      <c r="F510" t="n">
+        <v>0</v>
+      </c>
+      <c r="G510" t="n">
+        <v>1</v>
+      </c>
+      <c r="H510" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="511">
+      <c r="A511" s="2" t="n">
         <v>46082</v>
       </c>
-      <c r="B507" t="n">
+      <c r="B511" t="n">
         <v>65776.47</v>
       </c>
-      <c r="C507" t="n">
-        <v>9</v>
-      </c>
-      <c r="D507" t="n">
-        <v>3</v>
-      </c>
-      <c r="E507" t="n">
-        <v>7</v>
-      </c>
-      <c r="F507" t="n">
+      <c r="C511" t="n">
+        <v>1</v>
+      </c>
+      <c r="D511" t="n">
+        <v>3</v>
+      </c>
+      <c r="E511" t="n">
+        <v>6</v>
+      </c>
+      <c r="F511" t="n">
+        <v>0</v>
+      </c>
+      <c r="G511" t="n">
+        <v>1</v>
+      </c>
+      <c r="H511" t="n">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="512">
+      <c r="A512" s="2" t="n">
+        <v>46083</v>
+      </c>
+      <c r="B512" t="n">
+        <v>68830.06</v>
+      </c>
+      <c r="C512" t="n">
+        <v>3</v>
+      </c>
+      <c r="D512" t="n">
+        <v>6</v>
+      </c>
+      <c r="E512" t="n">
+        <v>6</v>
+      </c>
+      <c r="F512" t="n">
+        <v>0</v>
+      </c>
+      <c r="G512" t="n">
+        <v>2</v>
+      </c>
+      <c r="H512" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="513">
+      <c r="A513" s="2" t="n">
+        <v>46084</v>
+      </c>
+      <c r="B513" t="n">
+        <v>68338</v>
+      </c>
+      <c r="C513" t="n">
+        <v>7</v>
+      </c>
+      <c r="D513" t="n">
+        <v>1</v>
+      </c>
+      <c r="E513" t="n">
+        <v>6</v>
+      </c>
+      <c r="F513" t="n">
+        <v>0</v>
+      </c>
+      <c r="G513" t="n">
+        <v>2</v>
+      </c>
+      <c r="H513" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="514">
+      <c r="A514" s="2" t="n">
+        <v>46085</v>
+      </c>
+      <c r="B514" t="n">
+        <v>72666.77</v>
+      </c>
+      <c r="C514" t="n">
+        <v>3</v>
+      </c>
+      <c r="D514" t="n">
+        <v>6</v>
+      </c>
+      <c r="E514" t="n">
+        <v>0</v>
+      </c>
+      <c r="F514" t="n">
+        <v>10</v>
+      </c>
+      <c r="G514" t="n">
+        <v>2</v>
+      </c>
+      <c r="H514" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="515">
+      <c r="A515" s="2" t="n">
+        <v>46086</v>
+      </c>
+      <c r="B515" t="n">
+        <v>70890.72</v>
+      </c>
+      <c r="C515" t="n">
+        <v>7</v>
+      </c>
+      <c r="D515" t="n">
+        <v>1</v>
+      </c>
+      <c r="E515" t="n">
+        <v>0</v>
+      </c>
+      <c r="F515" t="n">
+        <v>2</v>
+      </c>
+      <c r="G515" t="n">
+        <v>11</v>
+      </c>
+      <c r="H515" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="516">
+      <c r="A516" s="2" t="n">
+        <v>46087</v>
+      </c>
+      <c r="B516" t="n">
+        <v>68114.02</v>
+      </c>
+      <c r="C516" t="n">
+        <v>7</v>
+      </c>
+      <c r="D516" t="n">
+        <v>1</v>
+      </c>
+      <c r="E516" t="n">
+        <v>11</v>
+      </c>
+      <c r="F516" t="n">
+        <v>2</v>
+      </c>
+      <c r="G516" t="n">
+        <v>11</v>
+      </c>
+      <c r="H516" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="517">
+      <c r="A517" s="2" t="n">
+        <v>46088</v>
+      </c>
+      <c r="B517" t="n">
+        <v>67262.91</v>
+      </c>
+      <c r="C517" t="n">
+        <v>7</v>
+      </c>
+      <c r="D517" t="n">
+        <v>1</v>
+      </c>
+      <c r="E517" t="n">
+        <v>6</v>
+      </c>
+      <c r="F517" t="n">
+        <v>2</v>
+      </c>
+      <c r="G517" t="n">
+        <v>11</v>
+      </c>
+      <c r="H517" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="518">
+      <c r="A518" s="2" t="n">
+        <v>46089</v>
+      </c>
+      <c r="B518" t="n">
+        <v>65971.2</v>
+      </c>
+      <c r="C518" t="n">
+        <v>7</v>
+      </c>
+      <c r="D518" t="n">
+        <v>1</v>
+      </c>
+      <c r="E518" t="n">
+        <v>11</v>
+      </c>
+      <c r="F518" t="n">
+        <v>2</v>
+      </c>
+      <c r="G518" t="n">
+        <v>11</v>
+      </c>
+      <c r="H518" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="519">
+      <c r="A519" s="2" t="n">
+        <v>46090</v>
+      </c>
+      <c r="B519" t="n">
+        <v>68432.16</v>
+      </c>
+      <c r="C519" t="n">
+        <v>7</v>
+      </c>
+      <c r="D519" t="n">
+        <v>1</v>
+      </c>
+      <c r="E519" t="n">
+        <v>11</v>
+      </c>
+      <c r="F519" t="n">
+        <v>2</v>
+      </c>
+      <c r="G519" t="n">
+        <v>11</v>
+      </c>
+      <c r="H519" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="520">
+      <c r="A520" s="2" t="n">
+        <v>46091</v>
+      </c>
+      <c r="B520" t="n">
+        <v>69948.63</v>
+      </c>
+      <c r="C520" t="n">
+        <v>3</v>
+      </c>
+      <c r="D520" t="n">
+        <v>6</v>
+      </c>
+      <c r="E520" t="n">
+        <v>0</v>
+      </c>
+      <c r="F520" t="n">
+        <v>10</v>
+      </c>
+      <c r="G520" t="n">
+        <v>2</v>
+      </c>
+      <c r="H520" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="521">
+      <c r="A521" s="2" t="n">
+        <v>46092</v>
+      </c>
+      <c r="B521" t="n">
+        <v>70191.86</v>
+      </c>
+      <c r="C521" t="n">
+        <v>7</v>
+      </c>
+      <c r="D521" t="n">
+        <v>1</v>
+      </c>
+      <c r="E521" t="n">
+        <v>11</v>
+      </c>
+      <c r="F521" t="n">
+        <v>2</v>
+      </c>
+      <c r="G521" t="n">
+        <v>11</v>
+      </c>
+      <c r="H521" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="522">
+      <c r="A522" s="2" t="n">
+        <v>46093</v>
+      </c>
+      <c r="B522" t="n">
+        <v>70541.34</v>
+      </c>
+      <c r="C522" t="n">
+        <v>7</v>
+      </c>
+      <c r="D522" t="n">
+        <v>1</v>
+      </c>
+      <c r="E522" t="n">
+        <v>6</v>
+      </c>
+      <c r="F522" t="n">
+        <v>2</v>
+      </c>
+      <c r="G522" t="n">
+        <v>11</v>
+      </c>
+      <c r="H522" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="523">
+      <c r="A523" s="2" t="n">
+        <v>46094</v>
+      </c>
+      <c r="B523" t="n">
+        <v>70930</v>
+      </c>
+      <c r="C523" t="n">
+        <v>3</v>
+      </c>
+      <c r="D523" t="n">
+        <v>6</v>
+      </c>
+      <c r="E523" t="n">
+        <v>0</v>
+      </c>
+      <c r="F523" t="n">
+        <v>10</v>
+      </c>
+      <c r="G523" t="n">
+        <v>2</v>
+      </c>
+      <c r="H523" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="524">
+      <c r="A524" s="2" t="n">
+        <v>46095</v>
+      </c>
+      <c r="B524" t="n">
+        <v>71211.95</v>
+      </c>
+      <c r="C524" t="n">
+        <v>7</v>
+      </c>
+      <c r="D524" t="n">
+        <v>1</v>
+      </c>
+      <c r="E524" t="n">
+        <v>6</v>
+      </c>
+      <c r="F524" t="n">
+        <v>0</v>
+      </c>
+      <c r="G524" t="n">
+        <v>11</v>
+      </c>
+      <c r="H524" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="525">
+      <c r="A525" s="2" t="n">
+        <v>46096</v>
+      </c>
+      <c r="B525" t="n">
+        <v>72815.24000000001</v>
+      </c>
+      <c r="C525" t="n">
+        <v>7</v>
+      </c>
+      <c r="D525" t="n">
+        <v>1</v>
+      </c>
+      <c r="E525" t="n">
+        <v>6</v>
+      </c>
+      <c r="F525" t="n">
+        <v>0</v>
+      </c>
+      <c r="G525" t="n">
+        <v>11</v>
+      </c>
+      <c r="H525" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="526">
+      <c r="A526" s="2" t="n">
+        <v>46097</v>
+      </c>
+      <c r="B526" t="n">
+        <v>74884.67</v>
+      </c>
+      <c r="C526" t="n">
+        <v>3</v>
+      </c>
+      <c r="D526" t="n">
+        <v>6</v>
+      </c>
+      <c r="E526" t="n">
+        <v>0</v>
+      </c>
+      <c r="F526" t="n">
+        <v>10</v>
+      </c>
+      <c r="G526" t="n">
+        <v>2</v>
+      </c>
+      <c r="H526" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="527">
+      <c r="A527" s="2" t="n">
+        <v>46098</v>
+      </c>
+      <c r="B527" t="n">
+        <v>73909.36</v>
+      </c>
+      <c r="C527" t="n">
+        <v>7</v>
+      </c>
+      <c r="D527" t="n">
+        <v>1</v>
+      </c>
+      <c r="E527" t="n">
+        <v>11</v>
+      </c>
+      <c r="F527" t="n">
+        <v>2</v>
+      </c>
+      <c r="G527" t="n">
+        <v>11</v>
+      </c>
+      <c r="H527" t="n">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="528">
+      <c r="A528" s="2" t="n">
+        <v>46099</v>
+      </c>
+      <c r="B528" t="n">
+        <v>71246.53999999999</v>
+      </c>
+      <c r="C528" t="n">
+        <v>7</v>
+      </c>
+      <c r="D528" t="n">
+        <v>1</v>
+      </c>
+      <c r="E528" t="n">
+        <v>11</v>
+      </c>
+      <c r="F528" t="n">
+        <v>2</v>
+      </c>
+      <c r="G528" t="n">
+        <v>11</v>
+      </c>
+      <c r="H528" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="529">
+      <c r="A529" s="2" t="n">
+        <v>46100</v>
+      </c>
+      <c r="B529" t="n">
+        <v>69930</v>
+      </c>
+      <c r="C529" t="n">
+        <v>7</v>
+      </c>
+      <c r="D529" t="n">
+        <v>1</v>
+      </c>
+      <c r="E529" t="n">
+        <v>11</v>
+      </c>
+      <c r="F529" t="n">
+        <v>2</v>
+      </c>
+      <c r="G529" t="n">
+        <v>11</v>
+      </c>
+      <c r="H529" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="530">
+      <c r="A530" s="2" t="n">
+        <v>46101</v>
+      </c>
+      <c r="B530" t="n">
+        <v>70510.73</v>
+      </c>
+      <c r="C530" t="n">
+        <v>7</v>
+      </c>
+      <c r="D530" t="n">
+        <v>1</v>
+      </c>
+      <c r="E530" t="n">
+        <v>11</v>
+      </c>
+      <c r="F530" t="n">
+        <v>2</v>
+      </c>
+      <c r="G530" t="n">
+        <v>11</v>
+      </c>
+      <c r="H530" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="531">
+      <c r="A531" s="2" t="n">
+        <v>46102</v>
+      </c>
+      <c r="B531" t="n">
+        <v>68918.12</v>
+      </c>
+      <c r="C531" t="n">
+        <v>7</v>
+      </c>
+      <c r="D531" t="n">
+        <v>1</v>
+      </c>
+      <c r="E531" t="n">
+        <v>11</v>
+      </c>
+      <c r="F531" t="n">
+        <v>7</v>
+      </c>
+      <c r="G531" t="n">
+        <v>7</v>
+      </c>
+      <c r="H531" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="532">
+      <c r="A532" s="2" t="n">
+        <v>46103</v>
+      </c>
+      <c r="B532" t="n">
+        <v>67859</v>
+      </c>
+      <c r="C532" t="n">
+        <v>4</v>
+      </c>
+      <c r="D532" t="n">
+        <v>8</v>
+      </c>
+      <c r="E532" t="n">
+        <v>2</v>
+      </c>
+      <c r="F532" t="n">
+        <v>7</v>
+      </c>
+      <c r="G532" t="n">
+        <v>7</v>
+      </c>
+      <c r="H532" t="n">
+        <v>6</v>
+      </c>
+    </row>
+    <row r="533">
+      <c r="A533" s="2" t="n">
+        <v>46104</v>
+      </c>
+      <c r="B533" t="n">
+        <v>70906.45</v>
+      </c>
+      <c r="C533" t="n">
+        <v>4</v>
+      </c>
+      <c r="D533" t="n">
+        <v>8</v>
+      </c>
+      <c r="E533" t="n">
+        <v>2</v>
+      </c>
+      <c r="F533" t="n">
+        <v>2</v>
+      </c>
+      <c r="G533" t="n">
+        <v>2</v>
+      </c>
+      <c r="H533" t="n">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="534">
+      <c r="A534" s="2" t="n">
+        <v>46105</v>
+      </c>
+      <c r="B534" t="n">
+        <v>70556.74000000001</v>
+      </c>
+      <c r="C534" t="n">
+        <v>7</v>
+      </c>
+      <c r="D534" t="n">
+        <v>1</v>
+      </c>
+      <c r="E534" t="n">
+        <v>6</v>
+      </c>
+      <c r="F534" t="n">
+        <v>7</v>
+      </c>
+      <c r="G534" t="n">
+        <v>7</v>
+      </c>
+      <c r="H534" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="535">
+      <c r="A535" s="2" t="n">
+        <v>46106</v>
+      </c>
+      <c r="B535" t="n">
+        <v>71336.53</v>
+      </c>
+      <c r="C535" t="n">
+        <v>7</v>
+      </c>
+      <c r="D535" t="n">
+        <v>1</v>
+      </c>
+      <c r="E535" t="n">
+        <v>6</v>
+      </c>
+      <c r="F535" t="n">
+        <v>7</v>
+      </c>
+      <c r="G535" t="n">
+        <v>7</v>
+      </c>
+      <c r="H535" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="536">
+      <c r="A536" s="2" t="n">
+        <v>46107</v>
+      </c>
+      <c r="B536" t="n">
+        <v>68820.31</v>
+      </c>
+      <c r="C536" t="n">
+        <v>7</v>
+      </c>
+      <c r="D536" t="n">
+        <v>3</v>
+      </c>
+      <c r="E536" t="n">
+        <v>6</v>
+      </c>
+      <c r="F536" t="n">
+        <v>7</v>
+      </c>
+      <c r="G536" t="n">
+        <v>7</v>
+      </c>
+      <c r="H536" t="n">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="537">
+      <c r="A537" s="2" t="n">
+        <v>46108</v>
+      </c>
+      <c r="B537" t="n">
+        <v>66407.28</v>
+      </c>
+      <c r="C537" t="n">
+        <v>5</v>
+      </c>
+      <c r="D537" t="n">
+        <v>9</v>
+      </c>
+      <c r="E537" t="n">
+        <v>3</v>
+      </c>
+      <c r="F537" t="n">
+        <v>5</v>
+      </c>
+      <c r="G537" t="n">
+        <v>13</v>
+      </c>
+      <c r="H537" t="n">
         <v>12</v>
       </c>
-      <c r="G507" t="n">
-        <v>1</v>
-      </c>
-      <c r="H507" t="n">
-        <v>10</v>
+    </row>
+    <row r="538">
+      <c r="A538" s="2" t="n">
+        <v>46109</v>
+      </c>
+      <c r="B538" t="n">
+        <v>66377.03</v>
+      </c>
+      <c r="C538" t="n">
+        <v>0</v>
+      </c>
+      <c r="D538" t="n">
+        <v>9</v>
+      </c>
+      <c r="E538" t="n">
+        <v>3</v>
+      </c>
+      <c r="F538" t="n">
+        <v>3</v>
+      </c>
+      <c r="G538" t="n">
+        <v>4</v>
+      </c>
+      <c r="H538" t="n">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
